--- a/data/trans_orig/IP31KM13_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM13_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34841</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31800</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36429</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>45257</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41861</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>41573</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>38493</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>90,19%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41366</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36886</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43689</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>155</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86622</t>
+          <t>76414</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81651</t>
+          <t>72816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>78330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2594</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5635</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4634</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3919</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8399</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>141621</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>133914</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>147206</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>85,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>149485</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>143963</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>153567</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>165420</t>
+          <t>136242</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157684</t>
+          <t>131444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171407</t>
+          <t>139902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>314906</t>
+          <t>277863</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>304886</t>
+          <t>268729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321821</t>
+          <t>284220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15421</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9836</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23128</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9814</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5732</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15336</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>185070</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>176922</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>192168</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>157325</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>145407</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>163428</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>197515</t>
+          <t>161017</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189477</t>
+          <t>154176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203717</t>
+          <t>166159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>354840</t>
+          <t>346086</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339729</t>
+          <t>334772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363572</t>
+          <t>354346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15056</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23204</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15747</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9644</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27665</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23013</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>28712</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>264480</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>237418</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>275330</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>251086</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>241564</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>259642</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>274892</t>
+          <t>230972</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>230030</t>
+          <t>221516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287866</t>
+          <t>239497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>525978</t>
+          <t>495452</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>485419</t>
+          <t>465779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>542667</t>
+          <t>508950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27741</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16891</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54803</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23181</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14625</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32703</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53288</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93847</t>
+          <t>81779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>626011</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>595829</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>640733</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>603153</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>586492</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>613665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638897</t>
+          <t>557527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>695737</t>
+          <t>579751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1282346</t>
+          <t>1195814</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1247065</t>
+          <t>1168873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1302456</t>
+          <t>1214604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60813</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>46091</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>90995</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39469</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>66642</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105836</t>
+          <t>60681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>115521</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95411</t>
+          <t>90427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150802</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
